--- a/Curso_Comunidades_2017/Abiot.xlsx
+++ b/Curso_Comunidades_2017/Abiot.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="17">
   <si>
-    <t xml:space="preserve">substrato</t>
+    <t xml:space="preserve">Substrato</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
@@ -380,7 +380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>11</v>
       </c>
@@ -400,10 +400,10 @@
         <v>16</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
@@ -417,16 +417,16 @@
         <v>14</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>11</v>
       </c>
@@ -446,10 +446,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>11</v>
       </c>
@@ -463,16 +463,16 @@
         <v>10</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>11</v>
       </c>
@@ -486,16 +486,16 @@
         <v>13</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
@@ -515,10 +515,10 @@
         <v>17</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>11</v>
       </c>
@@ -532,16 +532,16 @@
         <v>12</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>28</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>11</v>
       </c>
@@ -555,16 +555,16 @@
         <v>12</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>11</v>
       </c>
@@ -578,16 +578,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>15</v>
       </c>
@@ -601,16 +601,16 @@
         <v>7</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" s="0" t="n">
         <v>23</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>15</v>
       </c>
@@ -624,16 +624,16 @@
         <v>7</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F12" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>15</v>
       </c>
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>15</v>
       </c>
@@ -670,16 +670,16 @@
         <v>5</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>21</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>15</v>
       </c>
@@ -693,7 +693,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>21</v>
@@ -702,7 +702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>15</v>
       </c>
@@ -716,16 +716,16 @@
         <v>6</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>20</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>15</v>
       </c>
@@ -739,16 +739,16 @@
         <v>8</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G17" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>15</v>
       </c>
@@ -768,10 +768,10 @@
         <v>20</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>15</v>
       </c>
@@ -794,7 +794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>16</v>
       </c>
@@ -814,10 +814,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>16</v>
       </c>
@@ -840,7 +840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>16</v>
       </c>
@@ -854,16 +854,16 @@
         <v>4</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G22" s="0" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>16</v>
       </c>
@@ -883,10 +883,10 @@
         <v>17</v>
       </c>
       <c r="G23" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>16</v>
       </c>
@@ -909,7 +909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>16</v>
       </c>
@@ -923,7 +923,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" s="0" t="n">
         <v>12</v>
@@ -932,7 +932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>16</v>
       </c>
@@ -955,7 +955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>16</v>
       </c>
@@ -969,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" s="0" t="n">
         <v>11</v>
@@ -978,7 +978,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>16</v>
       </c>
@@ -995,10 +995,10 @@
         <v>10</v>
       </c>
       <c r="F28" s="0" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G28" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
